--- a/tests/fixtures/annual_fixture.xlsx
+++ b/tests/fixtures/annual_fixture.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -823,35 +823,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2023/24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>All Health Authorities</t>
+          <t>Fraser</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>All Facilities</t>
+          <t>Mission Memorial Hospital</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>All Procedures</t>
+          <t>Cataract Surgery</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>95200</v>
+        <v>41</v>
       </c>
       <c r="F13" t="n">
-        <v>289812</v>
+        <v>130</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H13" t="n">
-        <v>29.1</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="14">
@@ -872,20 +872,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>All Other Procedures</t>
+          <t>All Procedures</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2103</v>
+        <v>95200</v>
       </c>
       <c r="F14" t="n">
-        <v>9345</v>
+        <v>289812</v>
       </c>
       <c r="G14" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>19.2</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="15">
@@ -896,7 +896,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Interior</t>
+          <t>All Health Authorities</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -906,20 +906,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cataract Surgery</t>
+          <t>All Other Procedures</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4102</v>
+        <v>2103</v>
       </c>
       <c r="F15" t="n">
-        <v>12050</v>
+        <v>9345</v>
       </c>
       <c r="G15" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="H15" t="n">
-        <v>21.7</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="16">
@@ -935,19 +935,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Elk Valley Hospital</t>
+          <t>All Facilities</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Uterine Surgery</t>
+          <t>Cataract Surgery</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>8</v>
+        <v>4102</v>
       </c>
       <c r="F16" t="n">
-        <v>31</v>
+        <v>12050</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>21.7</v>
       </c>
     </row>
     <row r="17">
@@ -958,31 +964,59 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>Interior</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Elk Valley Hospital</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Uterine Surgery</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F17" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2024/25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>Northern</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>G.R. Baker Memorial Hospital</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Dental Surgery</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>&lt;5</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="F18" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="18"/>
     <row r="19"/>
     <row r="20"/>
+    <row r="21"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
